--- a/NTu/Mumberes_Maize_results.xlsx
+++ b/NTu/Mumberes_Maize_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>96.22252561063392</v>
+        <v>100.7717912581491</v>
       </c>
       <c r="C3" t="n">
         <v>113.649862435789</v>
       </c>
       <c r="D3" t="n">
-        <v>17.42733682515511</v>
+        <v>12.87807117763994</v>
       </c>
       <c r="E3" t="n">
-        <v>17.42747108732961</v>
+        <v>12.87820543981444</v>
       </c>
       <c r="F3" t="n">
-        <v>63.90072732020857</v>
+        <v>47.22008661265293</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05802976652502</v>
+        <v>94.01386512456698</v>
       </c>
       <c r="C4" t="n">
         <v>113.6498616437091</v>
       </c>
       <c r="D4" t="n">
-        <v>26.59183187718406</v>
+        <v>19.63599651914211</v>
       </c>
       <c r="E4" t="n">
-        <v>9.164495052028954</v>
+        <v>6.757925341502173</v>
       </c>
       <c r="F4" t="n">
-        <v>33.60314852410617</v>
+        <v>24.77905958550797</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>81.29241064165807</v>
+        <v>89.78450486055728</v>
       </c>
       <c r="C5" t="n">
         <v>113.6498609222855</v>
       </c>
       <c r="D5" t="n">
-        <v>32.35745028062743</v>
+        <v>23.86535606172822</v>
       </c>
       <c r="E5" t="n">
-        <v>5.765618403443369</v>
+        <v>4.22935954258611</v>
       </c>
       <c r="F5" t="n">
-        <v>21.14060081262569</v>
+        <v>15.50765165614907</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>77.33979125264993</v>
+        <v>86.91206770859019</v>
       </c>
       <c r="C6" t="n">
         <v>113.6498602652155</v>
       </c>
       <c r="D6" t="n">
-        <v>36.31006901256552</v>
+        <v>26.73779255662527</v>
       </c>
       <c r="E6" t="n">
-        <v>3.952618731938088</v>
+        <v>2.872436494897045</v>
       </c>
       <c r="F6" t="n">
-        <v>14.49293535043966</v>
+        <v>10.53226714795583</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>74.37962289937296</v>
+        <v>84.78916453521889</v>
       </c>
       <c r="C7" t="n">
         <v>113.6498596667584</v>
       </c>
       <c r="D7" t="n">
-        <v>39.27023676738546</v>
+        <v>28.86069513153953</v>
       </c>
       <c r="E7" t="n">
-        <v>2.960167754819935</v>
+        <v>2.122902574914264</v>
       </c>
       <c r="F7" t="n">
-        <v>10.85394843433976</v>
+        <v>7.783976108018966</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>71.98236749047616</v>
+        <v>83.09685647294081</v>
       </c>
       <c r="C8" t="n">
         <v>113.6498591216859</v>
       </c>
       <c r="D8" t="n">
-        <v>41.66749163120973</v>
+        <v>30.55300264874508</v>
       </c>
       <c r="E8" t="n">
-        <v>2.397254863824273</v>
+        <v>1.692307517205549</v>
       </c>
       <c r="F8" t="n">
-        <v>8.789934500689</v>
+        <v>6.205127563087014</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>69.9210216900707</v>
+        <v>81.66576556253217</v>
       </c>
       <c r="C9" t="n">
         <v>113.6498586252358</v>
       </c>
       <c r="D9" t="n">
-        <v>43.72883693516511</v>
+        <v>31.98409306270364</v>
       </c>
       <c r="E9" t="n">
-        <v>2.061345303955378</v>
+        <v>1.431090413958557</v>
       </c>
       <c r="F9" t="n">
-        <v>7.558266114503051</v>
+        <v>5.247331517848044</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>68.07436365552243</v>
+        <v>80.40474180600846</v>
       </c>
       <c r="C10" t="n">
         <v>113.6498581730708</v>
       </c>
       <c r="D10" t="n">
-        <v>45.57549451754839</v>
+        <v>33.24511636706237</v>
       </c>
       <c r="E10" t="n">
-        <v>1.846657582383287</v>
+        <v>1.26102330435873</v>
       </c>
       <c r="F10" t="n">
-        <v>6.771077802072052</v>
+        <v>4.62375211598201</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>66.37671635881021</v>
+        <v>79.26379807869166</v>
       </c>
       <c r="C11" t="n">
         <v>113.6498577612406</v>
       </c>
       <c r="D11" t="n">
-        <v>47.27314140243038</v>
+        <v>34.38605968254893</v>
       </c>
       <c r="E11" t="n">
-        <v>1.697646884881991</v>
+        <v>1.140943315486567</v>
       </c>
       <c r="F11" t="n">
-        <v>6.224705244567299</v>
+        <v>4.183458823450745</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>64.79169015923428</v>
+        <v>78.21471889215107</v>
       </c>
       <c r="C12" t="n">
         <v>113.6498573861471</v>
       </c>
       <c r="D12" t="n">
-        <v>48.85816722691284</v>
+        <v>35.43513849399605</v>
       </c>
       <c r="E12" t="n">
-        <v>1.585025824482457</v>
+        <v>1.049078811447117</v>
       </c>
       <c r="F12" t="n">
-        <v>5.811761356435677</v>
+        <v>3.84662230863943</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>63.2984047437878</v>
+        <v>77.2408733341354</v>
       </c>
       <c r="C13" t="n">
         <v>113.6498570445133</v>
       </c>
       <c r="D13" t="n">
-        <v>50.35145230072547</v>
+        <v>36.40898371037787</v>
       </c>
       <c r="E13" t="n">
-        <v>1.493285073812629</v>
+        <v>0.9738452163818181</v>
       </c>
       <c r="F13" t="n">
-        <v>5.47537860397964</v>
+        <v>3.5707657934</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>61.88424118719877</v>
+        <v>76.33184820263862</v>
       </c>
       <c r="C14" t="n">
         <v>113.6498567333544</v>
       </c>
       <c r="D14" t="n">
-        <v>51.76561554615558</v>
+        <v>37.31800853071573</v>
       </c>
       <c r="E14" t="n">
-        <v>1.41416324543011</v>
+        <v>0.9090248203378621</v>
       </c>
       <c r="F14" t="n">
-        <v>5.185265233243737</v>
+        <v>3.333091007905495</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>60.54102184913619</v>
+        <v>75.4806136929795</v>
       </c>
       <c r="C15" t="n">
         <v>113.649856449952</v>
       </c>
       <c r="D15" t="n">
-        <v>53.10883460081576</v>
+        <v>38.16924275697245</v>
       </c>
       <c r="E15" t="n">
-        <v>1.343219054660182</v>
+        <v>0.8512342262567216</v>
       </c>
       <c r="F15" t="n">
-        <v>4.925136533753999</v>
+        <v>3.121192162941313</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>59.26299303507039</v>
+        <v>74.68202236057674</v>
       </c>
       <c r="C16" t="n">
         <v>113.64985619183</v>
       </c>
       <c r="D16" t="n">
-        <v>54.38686315675965</v>
+        <v>38.9678338312533</v>
       </c>
       <c r="E16" t="n">
-        <v>1.278028555943884</v>
+        <v>0.79859107428085</v>
       </c>
       <c r="F16" t="n">
-        <v>4.686104705127573</v>
+        <v>2.928167272363117</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>58.04575693301815</v>
+        <v>73.93201096807624</v>
       </c>
       <c r="C17" t="n">
         <v>113.6498559567335</v>
       </c>
       <c r="D17" t="n">
-        <v>55.60409902371533</v>
+        <v>39.71784498865723</v>
       </c>
       <c r="E17" t="n">
-        <v>1.217235866955683</v>
+        <v>0.7500111574039323</v>
       </c>
       <c r="F17" t="n">
-        <v>4.463198178837504</v>
+        <v>2.750040910481085</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>56.88570388783223</v>
+        <v>73.22717333235592</v>
       </c>
       <c r="C18" t="n">
         <v>113.6498557426084</v>
       </c>
       <c r="D18" t="n">
-        <v>56.76415185477617</v>
+        <v>40.42268241025248</v>
       </c>
       <c r="E18" t="n">
-        <v>1.160052831060838</v>
+        <v>0.7048374215952435</v>
       </c>
       <c r="F18" t="n">
-        <v>4.253527047223074</v>
+        <v>2.58440387918256</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>55.77970864575744</v>
+        <v>72.56452926811052</v>
       </c>
       <c r="C19" t="n">
         <v>113.6498555475841</v>
       </c>
       <c r="D19" t="n">
-        <v>57.87014690182663</v>
+        <v>41.08532627947355</v>
       </c>
       <c r="E19" t="n">
-        <v>1.105995047050463</v>
+        <v>0.6626438692210712</v>
       </c>
       <c r="F19" t="n">
-        <v>4.055315172518365</v>
+        <v>2.429694187143928</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>54.72496604043216</v>
+        <v>71.94139738694817</v>
       </c>
       <c r="C20" t="n">
         <v>113.6498553699566</v>
       </c>
       <c r="D20" t="n">
-        <v>58.92488932952447</v>
+        <v>41.70845798300846</v>
       </c>
       <c r="E20" t="n">
-        <v>1.054742427697839</v>
+        <v>0.6231317035349093</v>
       </c>
       <c r="F20" t="n">
-        <v>3.867388901558743</v>
+        <v>2.284816246294668</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>53.71890047820741</v>
+        <v>71.35532307364629</v>
       </c>
       <c r="C21" t="n">
         <v>113.6498552081742</v>
       </c>
       <c r="D21" t="n">
-        <v>59.93095472996682</v>
+        <v>42.29453213452794</v>
       </c>
       <c r="E21" t="n">
-        <v>1.006065400442353</v>
+        <v>0.5860741515194832</v>
       </c>
       <c r="F21" t="n">
-        <v>3.688906468288626</v>
+        <v>2.148938555571438</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>52.75911460237632</v>
+        <v>70.80403593096874</v>
       </c>
       <c r="C22" t="n">
         <v>113.6498550608233</v>
       </c>
       <c r="D22" t="n">
-        <v>60.89074045844701</v>
+        <v>42.84581912985459</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9597857284801847</v>
+        <v>0.5512869953266488</v>
       </c>
       <c r="F22" t="n">
-        <v>3.519214337760677</v>
+        <v>2.021385649531046</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>51.84335886444914</v>
+        <v>70.28542310099576</v>
       </c>
       <c r="C23" t="n">
         <v>113.6498549266166</v>
       </c>
       <c r="D23" t="n">
-        <v>61.80649606216745</v>
+        <v>43.36443182562084</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9157556037204486</v>
+        <v>0.5186126957662509</v>
       </c>
       <c r="F23" t="n">
-        <v>3.357770546974978</v>
+        <v>1.901579884476253</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>50.96951234917274</v>
+        <v>69.79751126492739</v>
       </c>
       <c r="C24" t="n">
         <v>113.6498548043817</v>
       </c>
       <c r="D24" t="n">
-        <v>62.68034245520894</v>
+        <v>43.85234353945428</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8738463930414824</v>
+        <v>0.4879117138334408</v>
       </c>
       <c r="F24" t="n">
-        <v>3.204103441152102</v>
+        <v>1.789009617389283</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>50.13556974506722</v>
+        <v>69.33845349905897</v>
       </c>
       <c r="C25" t="n">
         <v>113.6498546930506</v>
       </c>
       <c r="D25" t="n">
-        <v>63.51428494798334</v>
+        <v>44.31140119399159</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8339424927744048</v>
+        <v>0.459057654537304</v>
       </c>
       <c r="F25" t="n">
-        <v>3.057789140172817</v>
+        <v>1.683211399970115</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>49.33963175016837</v>
+        <v>68.90651894798859</v>
       </c>
       <c r="C26" t="n">
         <v>113.6498545916505</v>
       </c>
       <c r="D26" t="n">
-        <v>64.31022284148216</v>
+        <v>44.74333564366194</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7959378934988166</v>
+        <v>0.4319344496703508</v>
       </c>
       <c r="F26" t="n">
-        <v>2.918438942828994</v>
+        <v>1.583759648791286</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>48.57989746854239</v>
+        <v>68.50008421915341</v>
       </c>
       <c r="C27" t="n">
         <v>113.6498544992957</v>
       </c>
       <c r="D27" t="n">
-        <v>65.06995703075333</v>
+        <v>45.14977028014232</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7597341892711711</v>
+        <v>0.4064346364803839</v>
       </c>
       <c r="F27" t="n">
-        <v>2.785692027327627</v>
+        <v>1.490260333761408</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>47.85465802203384</v>
+        <v>68.11762590223637</v>
       </c>
       <c r="C28" t="n">
         <v>113.6498544151793</v>
       </c>
       <c r="D28" t="n">
-        <v>65.79519639314546</v>
+        <v>45.53222851294294</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7252393623921307</v>
+        <v>0.3824582328006159</v>
       </c>
       <c r="F28" t="n">
-        <v>2.659210995437812</v>
+        <v>1.402346853602258</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>47.16229095568415</v>
+        <v>67.75771388216494</v>
       </c>
       <c r="C29" t="n">
         <v>113.6498543385664</v>
       </c>
       <c r="D29" t="n">
-        <v>66.48756338288223</v>
+        <v>45.89214045640145</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6923669897367688</v>
+        <v>0.3599119434585134</v>
       </c>
       <c r="F29" t="n">
-        <v>2.538678962368152</v>
+        <v>1.319677126014549</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>46.50125520304618</v>
+        <v>67.41900525581599</v>
       </c>
       <c r="C30" t="n">
         <v>113.6498542687876</v>
       </c>
       <c r="D30" t="n">
-        <v>67.14859906574139</v>
+        <v>46.23084901297158</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6610356828591648</v>
+        <v>0.3387085565701256</v>
       </c>
       <c r="F30" t="n">
-        <v>2.423797503816937</v>
+        <v>1.24193137409046</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>45.87008647765435</v>
+        <v>67.10023873845435</v>
       </c>
       <c r="C31" t="n">
         <v>113.6498542052333</v>
       </c>
       <c r="D31" t="n">
-        <v>67.77976772757896</v>
+        <v>46.54961546677896</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6311686618375631</v>
+        <v>0.3187664538073847</v>
       </c>
       <c r="F31" t="n">
-        <v>2.314285093404398</v>
+        <v>1.168810330627077</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>45.26739301056409</v>
+        <v>66.80022948716288</v>
       </c>
       <c r="C32" t="n">
         <v>113.6498541473483</v>
       </c>
       <c r="D32" t="n">
-        <v>68.38246113678424</v>
+        <v>46.84962466018546</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6026934092052869</v>
+        <v>0.3000091934064955</v>
       </c>
       <c r="F32" t="n">
-        <v>2.209875833752719</v>
+        <v>1.10003370915715</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>44.69185158297879</v>
+        <v>66.51786429133246</v>
       </c>
       <c r="C33" t="n">
         <v>113.6498540946269</v>
       </c>
       <c r="D33" t="n">
-        <v>68.95800251164806</v>
+        <v>47.1319898032944</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5755413748638176</v>
+        <v>0.2823651431089473</v>
       </c>
       <c r="F33" t="n">
-        <v>2.110318374500665</v>
+        <v>1.03533885806614</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>44.14220381906099</v>
+        <v>66.25209709326491</v>
       </c>
       <c r="C34" t="n">
         <v>113.6498540466084</v>
       </c>
       <c r="D34" t="n">
-        <v>69.5076502275474</v>
+        <v>47.39775695334347</v>
       </c>
       <c r="E34" t="n">
-        <v>0.54964771589934</v>
+        <v>0.2657671500490721</v>
       </c>
       <c r="F34" t="n">
-        <v>2.01537495829758</v>
+        <v>0.9744795501799312</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>43.61725271316318</v>
+        <v>66.00194480965681</v>
       </c>
       <c r="C35" t="n">
         <v>113.6498540028733</v>
       </c>
       <c r="D35" t="n">
-        <v>70.0326012897101</v>
+        <v>47.64790919321648</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5249510621626996</v>
+        <v>0.2501522398730032</v>
       </c>
       <c r="F35" t="n">
-        <v>1.924820561263232</v>
+        <v>0.917224879534345</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>43.11585937113041</v>
+        <v>65.76648342958035</v>
       </c>
       <c r="C36" t="n">
         <v>113.6498539630395</v>
       </c>
       <c r="D36" t="n">
-        <v>70.53399459190911</v>
+        <v>47.88337053345916</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5013933021990056</v>
+        <v>0.2354613402426793</v>
       </c>
       <c r="F36" t="n">
-        <v>1.83844210806302</v>
+        <v>0.8633582475564907</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>42.63693994872593</v>
+        <v>65.54484436784524</v>
       </c>
       <c r="C37" t="n">
         <v>113.6498539267591</v>
       </c>
       <c r="D37" t="n">
-        <v>71.01291397803311</v>
+        <v>48.10500955891381</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4789193861240051</v>
+        <v>0.2216390254546496</v>
       </c>
       <c r="F37" t="n">
-        <v>1.756037749121352</v>
+        <v>0.8126764266670486</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>42.17946277251595</v>
+        <v>65.3362110549934</v>
       </c>
       <c r="C38" t="n">
         <v>113.6498538937149</v>
       </c>
       <c r="D38" t="n">
-        <v>71.47039112119899</v>
+        <v>48.31364283872153</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4574771431658746</v>
+        <v>0.2086332798077279</v>
       </c>
       <c r="F38" t="n">
-        <v>1.677416191608207</v>
+        <v>0.7649886926283358</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>41.74244563020336</v>
+        <v>65.13981574701508</v>
       </c>
       <c r="C39" t="n">
         <v>113.6498538636185</v>
       </c>
       <c r="D39" t="n">
-        <v>71.9074082334152</v>
+        <v>48.51003811660347</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4370171122162105</v>
+        <v>0.1963952778819333</v>
       </c>
       <c r="F39" t="n">
-        <v>1.602396078126105</v>
+        <v>0.7201160189004222</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>41.32495321868049</v>
+        <v>64.95493653938004</v>
       </c>
       <c r="C40" t="n">
         <v>113.6498538362068</v>
       </c>
       <c r="D40" t="n">
-        <v>72.3249006175263</v>
+        <v>48.69491729682674</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4174923841110996</v>
+        <v>0.1848791802232768</v>
       </c>
       <c r="F40" t="n">
-        <v>1.530805408407365</v>
+        <v>0.6778903274853482</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>40.92609473912009</v>
+        <v>64.78089457126038</v>
       </c>
       <c r="C41" t="n">
         <v>113.6498538112403</v>
       </c>
       <c r="D41" t="n">
-        <v>72.72375907212023</v>
+        <v>48.86895923997994</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3988584545939347</v>
+        <v>0.174041943153199</v>
       </c>
       <c r="F41" t="n">
-        <v>1.46248100017776</v>
+        <v>0.6381537915617296</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>40.54502162931571</v>
+        <v>64.61705140694629</v>
       </c>
       <c r="C42" t="n">
         <v>113.6498537885009</v>
       </c>
       <c r="D42" t="n">
-        <v>73.10483215918521</v>
+        <v>49.03280238155463</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3810730870649763</v>
+        <v>0.1638431415746879</v>
       </c>
       <c r="F42" t="n">
-        <v>1.397267985904913</v>
+        <v>0.6007581857738558</v>
       </c>
     </row>
   </sheetData>
